--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484695_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484695_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5123</v>
+        <v>8.305199999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4143</v>
+        <v>6.8514</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0979</v>
+        <v>1.4538</v>
       </c>
       <c r="G2" t="n">
         <v>5.0766</v>
@@ -610,13 +610,13 @@
         <v>2.5656</v>
       </c>
       <c r="S2" t="n">
-        <v>2.192</v>
+        <v>0.9849</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7851</v>
+        <v>0.2221</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4069</v>
+        <v>0.7628</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3219</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8285</v>
+        <v>3.2157</v>
       </c>
       <c r="E3" t="n">
-        <v>4.729</v>
+        <v>5.2648</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9005</v>
+        <v>-2.0491</v>
       </c>
       <c r="G3" t="n">
         <v>4.021</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6481</v>
+        <v>-0.2609</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6244</v>
+        <v>-0.0886</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0237</v>
+        <v>-0.1723</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2774</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4382</v>
+        <v>2.5323</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7643</v>
+        <v>1.586</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6738</v>
+        <v>0.9463</v>
       </c>
       <c r="G4" t="n">
         <v>1.9518</v>
@@ -766,13 +766,13 @@
         <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3145</v>
+        <v>-0.2204</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2398</v>
+        <v>-0.4182</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0747</v>
+        <v>0.1978</v>
       </c>
       <c r="V4" t="n">
         <v>1.9005</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0446</v>
+        <v>-1.8526</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0154</v>
+        <v>0.4243</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0292</v>
+        <v>-2.277</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4225</v>
@@ -922,13 +922,13 @@
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9336</v>
+        <v>-0.7417</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.3311</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1629</v>
+        <v>-0.4107</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3219</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3325</v>
+        <v>-2.6898</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.2454</v>
+        <v>-3.4788</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9129</v>
+        <v>0.789</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2891</v>
@@ -1000,13 +1000,13 @@
         <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8337</v>
+        <v>0.4764</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2919</v>
+        <v>0.0585</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.418</v>
       </c>
       <c r="V7" t="n">
         <v>0.3219</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ESTARLICH MARTINEZ</t>
+          <t>I. EGIDO MUNOZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1249</v>
+        <v>-3.3847</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7056</v>
+        <v>-1.8432</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4193</v>
+        <v>-1.5415</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.3596</v>
+        <v>-3.7289</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.4013</v>
+        <v>-2.8283</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0417</v>
+        <v>-0.9006</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4364</v>
+        <v>-1.2696</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4462</v>
+        <v>-0.0808</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0098</v>
+        <v>-1.1889</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.9232</v>
+        <v>-2.4593</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.9551</v>
+        <v>-2.7475</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0318</v>
+        <v>0.2882</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0377</v>
+        <v>-0.161</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7308</v>
+        <v>0.0208</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7685</v>
+        <v>-0.1818</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0104</v>
+        <v>0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2875</v>
+        <v>-3.4189</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3535</v>
+        <v>-2.6831</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.7358</v>
       </c>
       <c r="G9" t="n">
         <v>-3.3086</v>
@@ -1156,13 +1156,13 @@
         <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4609</v>
+        <v>0.3296</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6946</v>
+        <v>0.365</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2336</v>
+        <v>-0.0355</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6231</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. EGIDO MUNOZ</t>
+          <t>J. ESTARLICH MARTINEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5033</v>
+        <v>-3.5096</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7636</v>
+        <v>-1.0902</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7397</v>
+        <v>-2.4193</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.7289</v>
+        <v>-4.3596</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8283</v>
+        <v>-4.4013</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9006</v>
+        <v>0.0417</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2696</v>
+        <v>-1.4364</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0808</v>
+        <v>-1.4462</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1889</v>
+        <v>0.0098</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4593</v>
+        <v>-2.9232</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.7475</v>
+        <v>-2.9551</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2882</v>
+        <v>0.0318</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0995</v>
+        <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2796</v>
+        <v>-0.4223</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8997000000000001</v>
+        <v>0.3462</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.38</v>
+        <v>-0.7685</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3219</v>
+        <v>-0.0104</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0109</v>
+        <v>-4.9336</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1658</v>
+        <v>-1.2619</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8451</v>
+        <v>-3.6717</v>
       </c>
       <c r="G11" t="n">
         <v>-4.4214</v>
@@ -1312,13 +1312,13 @@
         <v>0.1833</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8014</v>
+        <v>-0.7242</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2549</v>
+        <v>0.1588</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0563</v>
+        <v>-0.8829</v>
       </c>
       <c r="V11" t="n">
         <v>0.945</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4737</v>
+        <v>-5.0643</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5434</v>
+        <v>-2.1588</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9303</v>
+        <v>-2.9055</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4743</v>
@@ -1390,13 +1390,13 @@
         <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5333</v>
+        <v>-0.1239</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3673</v>
+        <v>0.0174</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.166</v>
+        <v>-0.1412</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6829</v>
+        <v>-5.3885</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8828</v>
+        <v>-3.7867</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8</v>
+        <v>-1.6018</v>
       </c>
       <c r="G13" t="n">
         <v>-3.3745</v>
@@ -1468,13 +1468,13 @@
         <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5466</v>
+        <v>-0.2523</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4201</v>
+        <v>0.5162</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9667</v>
+        <v>-0.7685</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5785</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.578</v>
+        <v>-6.52</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.8092</v>
+        <v>-1.8503</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.7688</v>
+        <v>-4.6697</v>
       </c>
       <c r="G14" t="n">
         <v>-3.7165</v>
@@ -1546,13 +1546,13 @@
         <v>1.0995</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.228</v>
+        <v>-0.1701</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0717</v>
+        <v>0.0306</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2997</v>
+        <v>-0.2006</v>
       </c>
       <c r="V14" t="n">
         <v>-1.9005</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-22.9342</v>
+        <v>-22.3837</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.252000000000002</v>
+        <v>-3.701400000000001</v>
       </c>
       <c r="F15" t="n">
         <v>-18.6823</v>
@@ -1624,10 +1624,10 @@
         <v>13.7442</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8362</v>
+        <v>-1.2859</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3471999999999998</v>
+        <v>0.8976999999999999</v>
       </c>
       <c r="U15" t="n">
         <v>-2.1834</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9685</v>
+        <v>7.342</v>
       </c>
       <c r="E16" t="n">
-        <v>7.0342</v>
+        <v>6.0727</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9342</v>
+        <v>1.2693</v>
       </c>
       <c r="G16" t="n">
         <v>5.8862</v>
@@ -1702,13 +1702,13 @@
         <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7445</v>
+        <v>1.118</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8484</v>
+        <v>0.8869</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1039</v>
+        <v>0.2311</v>
       </c>
       <c r="V16" t="n">
         <v>-0.945</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8468</v>
+        <v>6.3813</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7492</v>
+        <v>4.5184</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0976</v>
+        <v>1.8629</v>
       </c>
       <c r="G17" t="n">
         <v>5.0366</v>
@@ -1780,13 +1780,13 @@
         <v>1.8326</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1165</v>
+        <v>0.418</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.101</v>
+        <v>-0.3318</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9845</v>
+        <v>0.7498</v>
       </c>
       <c r="V17" t="n">
         <v>0.0104</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>A. RUIZ FRAGUEIRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.2674</v>
+        <v>3.3064</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2421</v>
+        <v>1.8953</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0253</v>
+        <v>1.4111</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6704</v>
+        <v>2.4362</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7919</v>
+        <v>2.4073</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1215</v>
+        <v>0.0289</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.1998</v>
+        <v>2.4091</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.8088</v>
+        <v>2.9569</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.391</v>
+        <v>-0.5478</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4706</v>
+        <v>0.0271</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9831</v>
+        <v>-0.5496</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5125</v>
+        <v>0.5768</v>
       </c>
       <c r="P18" t="n">
         <v>0.5498</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3823</v>
+        <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8986</v>
+        <v>0.632</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5181</v>
+        <v>0.7036</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3805</v>
+        <v>-0.0717</v>
       </c>
       <c r="V18" t="n">
-        <v>3.4894</v>
+        <v>-0.3115</v>
       </c>
       <c r="W18" t="n">
-        <v>4.7563</v>
+        <v>-0.3011</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.267</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RUIZ FRAGUEIRO</t>
+          <t>J. CARRERAS MUNOZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4322</v>
+        <v>3.1375</v>
       </c>
       <c r="E19" t="n">
-        <v>1.703</v>
+        <v>3.1012</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7292</v>
+        <v>0.0362</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4362</v>
+        <v>3.5692</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4073</v>
+        <v>0.1296</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0289</v>
+        <v>3.4396</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4091</v>
+        <v>5.4028</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9569</v>
+        <v>1.418</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5478</v>
+        <v>3.9848</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0271</v>
+        <v>-1.8336</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5496</v>
+        <v>-1.2884</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5768</v>
+        <v>-0.5452</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4661</v>
+        <v>2.1991</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2422</v>
+        <v>-0.1648</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5113</v>
+        <v>-0.4691</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7536</v>
+        <v>0.3043</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3115</v>
+        <v>-0.6335</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0104</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUNOZ</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.9864</v>
+        <v>2.4137</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5243</v>
+        <v>1.2806</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5379</v>
+        <v>1.1331</v>
       </c>
       <c r="G20" t="n">
-        <v>3.5692</v>
+        <v>-2.6704</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1296</v>
+        <v>-2.7919</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4396</v>
+        <v>0.1215</v>
       </c>
       <c r="J20" t="n">
-        <v>5.4028</v>
+        <v>-2.1998</v>
       </c>
       <c r="K20" t="n">
-        <v>1.418</v>
+        <v>-1.8088</v>
       </c>
       <c r="L20" t="n">
-        <v>3.9848</v>
+        <v>-0.391</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8336</v>
+        <v>-0.4706</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2884</v>
+        <v>-0.9831</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5452</v>
+        <v>0.5125</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1991</v>
+        <v>2.3823</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3158</v>
+        <v>1.0449</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.046</v>
+        <v>0.5566</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2698</v>
+        <v>0.4883</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6335</v>
+        <v>3.4894</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4.7563</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6335</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. DE LA IGLESIA SANTAMARIA</t>
+          <t>A. ORTEGA IBAÑEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4514</v>
+        <v>1.3005</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5845</v>
+        <v>1.3005</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8669</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9923999999999999</v>
+        <v>1.3005</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6752</v>
+        <v>1.3005</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3172</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6856</v>
+        <v>1.3005</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5605</v>
+        <v>1.3005</v>
       </c>
       <c r="L21" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6932</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8854</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1922</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9641999999999999</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7315</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2327</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBAÑEZ</t>
+          <t>I. DE LA IGLESIA SANTAMARIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.3005</v>
+        <v>0.854</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3005</v>
+        <v>0.0076</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.8464</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3005</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3005</v>
+        <v>0.6752</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.3172</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3005</v>
+        <v>1.6856</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3005</v>
+        <v>1.5605</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-0.6932</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.8854</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.1922</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.3669</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.1546</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.2123</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="23">
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. PALAU LOPEZ</t>
+          <t>J. MATEO LAZARO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5085</v>
+        <v>0.322</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3268</v>
+        <v>2.3939</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8183</v>
+        <v>-2.0719</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.709</v>
+        <v>2.0973</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0037</v>
+        <v>1.6325</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7053</v>
+        <v>0.4648</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3901</v>
+        <v>4.427</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3901</v>
+        <v>3.0003</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.4268</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0991</v>
+        <v>-2.3297</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3938</v>
+        <v>-1.3677</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7053</v>
+        <v>-0.962</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.733</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1833</v>
+        <v>1.8326</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6835</v>
+        <v>-0.2151</v>
       </c>
       <c r="T25" t="n">
-        <v>0.586</v>
+        <v>-0.5513</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0975</v>
+        <v>0.3361</v>
       </c>
       <c r="V25" t="n">
-        <v>1.267</v>
+        <v>-0.6439</v>
       </c>
       <c r="W25" t="n">
         <v>1.267</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. MATEO LAZARO</t>
+          <t>I. RUIPEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4138</v>
+        <v>0.1965</v>
       </c>
       <c r="E26" t="n">
-        <v>2.0093</v>
+        <v>-1.4643</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.423</v>
+        <v>1.6608</v>
       </c>
       <c r="G26" t="n">
-        <v>2.0973</v>
+        <v>-0.2481</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6325</v>
+        <v>0.7582</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4648</v>
+        <v>-1.0062</v>
       </c>
       <c r="J26" t="n">
-        <v>4.427</v>
+        <v>-0.9179</v>
       </c>
       <c r="K26" t="n">
-        <v>3.0003</v>
+        <v>0.9537</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4268</v>
+        <v>-1.8716</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.3297</v>
+        <v>0.6698</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.3677</v>
+        <v>-0.1955</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.962</v>
+        <v>0.8653</v>
       </c>
       <c r="P26" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="Q26" t="n">
         <v>-0.9163</v>
       </c>
-      <c r="Q26" t="n">
-        <v>-2.7489</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.8326</v>
+        <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9509</v>
+        <v>0.2613</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9359</v>
+        <v>0.3699</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.015</v>
+        <v>-0.1086</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>I. RUIPEREZ SANCHEZ</t>
+          <t>A. PALAU LOPEZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,64 +2515,64 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.2517</v>
+        <v>0.0495</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.3296</v>
+        <v>0.9422</v>
       </c>
       <c r="F27" t="n">
-        <v>1.078</v>
+        <v>-0.8927</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2481</v>
+        <v>-0.709</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7582</v>
+        <v>-0.0037</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.0062</v>
+        <v>-0.7053</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9179</v>
+        <v>0.3901</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9537</v>
+        <v>0.3901</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.8716</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6698</v>
+        <v>-1.0991</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.1955</v>
+        <v>-0.3938</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8653</v>
+        <v>-0.7053</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1833</v>
+        <v>-0.733</v>
       </c>
       <c r="Q27" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R27" t="n">
-        <v>1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.1869</v>
+        <v>0.2245</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4955</v>
+        <v>0.2014</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.6914</v>
+        <v>0.0232</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.4624</v>
+        <v>-1.1055</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.7624</v>
+        <v>-2.6663</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3</v>
+        <v>1.5608</v>
       </c>
       <c r="G28" t="n">
         <v>-2.2704</v>
@@ -2638,13 +2638,13 @@
         <v>1.6493</v>
       </c>
       <c r="S28" t="n">
-        <v>0.3578</v>
+        <v>0.7147</v>
       </c>
       <c r="T28" t="n">
-        <v>0.5664</v>
+        <v>0.6625</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.2085</v>
+        <v>0.0522</v>
       </c>
       <c r="V28" t="n">
         <v>0.6335</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>22.93420000000001</v>
+        <v>25.4983</v>
       </c>
       <c r="E29" t="n">
-        <v>18.6823</v>
+        <v>18.6822</v>
       </c>
       <c r="F29" t="n">
-        <v>4.252000000000001</v>
+        <v>6.816000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>16.7209</v>
@@ -2686,7 +2686,7 @@
         <v>14.6372</v>
       </c>
       <c r="I29" t="n">
-        <v>2.0837</v>
+        <v>2.083699999999999</v>
       </c>
       <c r="J29" t="n">
         <v>21.6546</v>
@@ -2716,22 +2716,22 @@
         <v>15.5769</v>
       </c>
       <c r="S29" t="n">
-        <v>1.8363</v>
+        <v>4.400399999999999</v>
       </c>
       <c r="T29" t="n">
         <v>2.1833</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.347</v>
+        <v>2.217</v>
       </c>
       <c r="V29" t="n">
-        <v>2.544499999999999</v>
+        <v>2.5445</v>
       </c>
       <c r="W29" t="n">
         <v>8.5885</v>
       </c>
       <c r="X29" t="n">
-        <v>-6.0442</v>
+        <v>-6.044199999999999</v>
       </c>
     </row>
   </sheetData>
